--- a/artfynd/A 24024-2023 artfynd.xlsx
+++ b/artfynd/A 24024-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24024-2023 artfynd.xlsx
+++ b/artfynd/A 24024-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96840182</v>
+        <v>54420897</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,26 +713,21 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Råaköp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410779.0245382369</v>
+        <v>410866</v>
       </c>
       <c r="R2" t="n">
-        <v>6282565.277834641</v>
+        <v>6282618</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en levande ek.</t>
+          <t>På en ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -812,12 +791,7 @@
         <v>96840256</v>
       </c>
       <c r="B3" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410743.1659698584</v>
+        <v>410743</v>
       </c>
       <c r="R3" t="n">
-        <v>6282639.667069301</v>
+        <v>6282640</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,19 +872,9 @@
           <t>2021-10-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,6 +904,238 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>54420898</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Råaköp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>410779</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6282506</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-07-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en ek</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96840182</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råaköp, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>410779</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6282565</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torpa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en levande ek.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24024-2023 artfynd.xlsx
+++ b/artfynd/A 24024-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96840256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54420897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54420898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96840182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>